--- a/Reports/EnvEveLog.xlsx
+++ b/Reports/EnvEveLog.xlsx
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>47.54223047222055</v>
+        <v>48.28256968706272</v>
       </c>
       <c r="G2" t="n">
-        <v>44.53193051558074</v>
+        <v>45.27226973042292</v>
       </c>
       <c r="H2" t="n">
         <v>1e-30</v>
@@ -586,28 +586,28 @@
         <v>2925.172973150331</v>
       </c>
       <c r="J2" t="n">
-        <v>46.82093326295253</v>
+        <v>47.5612724777947</v>
       </c>
       <c r="K2" t="n">
         <v>187.8778416538028</v>
       </c>
       <c r="L2" t="n">
-        <v>1.082064662563559</v>
+        <v>1.154909257789952</v>
       </c>
       <c r="M2" t="n">
-        <v>157.5479917579363</v>
+        <v>-149.4838752617311</v>
       </c>
       <c r="N2" t="n">
-        <v>16.82093326295253</v>
+        <v>17.5612724777947</v>
       </c>
       <c r="O2" t="n">
         <v>30</v>
       </c>
       <c r="P2" t="n">
-        <v>-141.0569083908502</v>
+        <v>-140.316569176008</v>
       </c>
       <c r="Q2" t="n">
-        <v>-141.0569083908502</v>
+        <v>-140.316569176008</v>
       </c>
       <c r="R2" t="n">
         <v>3964.814485118334</v>
@@ -631,7 +631,7 @@
         <v>7.53563738904006</v>
       </c>
       <c r="Y2" t="n">
-        <v>163.9731205251298</v>
+        <v>164.9731205251298</v>
       </c>
       <c r="Z2" t="n">
         <v>1.055284896272219</v>
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>48.30316969076519</v>
+        <v>48.42652921601626</v>
       </c>
       <c r="G3" t="n">
-        <v>45.29286973412538</v>
+        <v>45.41622925937645</v>
       </c>
       <c r="H3" t="n">
         <v>1e-30</v>
@@ -668,28 +668,28 @@
         <v>2918.3103020424</v>
       </c>
       <c r="J3" t="n">
-        <v>47.56147080377735</v>
+        <v>47.68483032902843</v>
       </c>
       <c r="K3" t="n">
         <v>187.857439976083</v>
       </c>
       <c r="L3" t="n">
-        <v>1.084897493908163</v>
+        <v>1.156137948742218</v>
       </c>
       <c r="M3" t="n">
-        <v>157.5351863568948</v>
+        <v>-149.5962631333745</v>
       </c>
       <c r="N3" t="n">
-        <v>17.56147080377735</v>
+        <v>17.68483032902843</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>-140.2959691723056</v>
+        <v>-140.1726096470545</v>
       </c>
       <c r="Q3" t="n">
-        <v>-140.2959691723056</v>
+        <v>-140.1726096470545</v>
       </c>
       <c r="R3" t="n">
         <v>3971.024802073922</v>
@@ -713,10 +713,10 @@
         <v>7.535648199654293</v>
       </c>
       <c r="Y3" t="n">
-        <v>163.951872253482</v>
+        <v>164.951872253482</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.11916110502662</v>
+        <v>1.119161105026607</v>
       </c>
     </row>
     <row r="4">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>48.85477880728143</v>
+        <v>48.5394846242223</v>
       </c>
       <c r="G4" t="n">
-        <v>45.84447885064162</v>
+        <v>45.52918466758248</v>
       </c>
       <c r="H4" t="n">
         <v>1e-30</v>
@@ -750,28 +750,28 @@
         <v>2911.447771944785</v>
       </c>
       <c r="J4" t="n">
-        <v>48.09263063034305</v>
+        <v>47.77733644728391</v>
       </c>
       <c r="K4" t="n">
         <v>187.8369906861324</v>
       </c>
       <c r="L4" t="n">
-        <v>1.087750651386353</v>
+        <v>1.157380873373423</v>
       </c>
       <c r="M4" t="n">
-        <v>157.522428017705</v>
+        <v>-149.7092416202459</v>
       </c>
       <c r="N4" t="n">
-        <v>18.09263063034305</v>
+        <v>17.77733644728391</v>
       </c>
       <c r="O4" t="n">
         <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>-139.7443600557893</v>
+        <v>-140.0596542388485</v>
       </c>
       <c r="Q4" t="n">
-        <v>-139.7443600557893</v>
+        <v>-140.0596542388485</v>
       </c>
       <c r="R4" t="n">
         <v>3977.230532691764</v>
@@ -795,7 +795,7 @@
         <v>7.535659022502847</v>
       </c>
       <c r="Y4" t="n">
-        <v>163.9305370533707</v>
+        <v>164.9305370533707</v>
       </c>
       <c r="Z4" t="n">
         <v>1.183197228970331</v>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49.21931807021644</v>
+        <v>48.62112595952223</v>
       </c>
       <c r="G5" t="n">
-        <v>46.20901811357663</v>
+        <v>45.61082600288242</v>
       </c>
       <c r="H5" t="n">
         <v>1e-30</v>
@@ -832,28 +832,28 @@
         <v>2904.585393382574</v>
       </c>
       <c r="J5" t="n">
-        <v>48.43667279884535</v>
+        <v>47.83848068815115</v>
       </c>
       <c r="K5" t="n">
         <v>187.8164935916997</v>
       </c>
       <c r="L5" t="n">
-        <v>1.090624324669255</v>
+        <v>1.158638219836315</v>
       </c>
       <c r="M5" t="n">
-        <v>157.5097174537487</v>
+        <v>-149.8228125165609</v>
       </c>
       <c r="N5" t="n">
-        <v>18.43667279884535</v>
+        <v>17.83848068815115</v>
       </c>
       <c r="O5" t="n">
         <v>30</v>
       </c>
       <c r="P5" t="n">
-        <v>-139.3798207928544</v>
+        <v>-139.9780129035485</v>
       </c>
       <c r="Q5" t="n">
-        <v>-139.3798207928544</v>
+        <v>-139.9780129035485</v>
       </c>
       <c r="R5" t="n">
         <v>3983.431669203378</v>
@@ -877,7 +877,7 @@
         <v>7.535669857550016</v>
       </c>
       <c r="Y5" t="n">
-        <v>163.9091141611784</v>
+        <v>164.9091141611784</v>
       </c>
       <c r="Z5" t="n">
         <v>1.247394412869355</v>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49.40899309673646</v>
+        <v>48.67090385748054</v>
       </c>
       <c r="G6" t="n">
-        <v>46.39869314009665</v>
+        <v>45.66060390084073</v>
       </c>
       <c r="H6" t="n">
         <v>1e-30</v>
@@ -914,28 +914,28 @@
         <v>2897.72317588242</v>
       </c>
       <c r="J6" t="n">
-        <v>48.60580272992379</v>
+        <v>47.86771349066787</v>
       </c>
       <c r="K6" t="n">
         <v>187.7959484962581</v>
       </c>
       <c r="L6" t="n">
-        <v>1.093518679686076</v>
+        <v>1.159910256304858</v>
       </c>
       <c r="M6" t="n">
-        <v>157.4970615399377</v>
+        <v>-149.9369730445895</v>
       </c>
       <c r="N6" t="n">
-        <v>18.60580272992379</v>
+        <v>17.86771349066787</v>
       </c>
       <c r="O6" t="n">
         <v>30</v>
       </c>
       <c r="P6" t="n">
-        <v>-139.1901457663343</v>
+        <v>-139.9282350055902</v>
       </c>
       <c r="Q6" t="n">
-        <v>-139.1901457663343</v>
+        <v>-139.9282350055902</v>
       </c>
       <c r="R6" t="n">
         <v>3989.628204424113</v>
@@ -959,10 +959,10 @@
         <v>7.535680704760108</v>
       </c>
       <c r="Y6" t="n">
-        <v>163.8876029772208</v>
+        <v>164.8876029772208</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.311753843689576</v>
+        <v>1.311753843689601</v>
       </c>
     </row>
     <row r="7">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>49.42828516210476</v>
+        <v>48.68801086525132</v>
       </c>
       <c r="G7" t="n">
-        <v>46.41798520546495</v>
+        <v>45.67771090861151</v>
       </c>
       <c r="H7" t="n">
         <v>1e-30</v>
@@ -996,28 +996,28 @@
         <v>2890.861130146279</v>
       </c>
       <c r="J7" t="n">
-        <v>48.60450150452391</v>
+        <v>47.86422720767047</v>
       </c>
       <c r="K7" t="n">
         <v>187.7753552054899</v>
       </c>
       <c r="L7" t="n">
-        <v>1.096433910287685</v>
+        <v>1.161197176607411</v>
       </c>
       <c r="M7" t="n">
-        <v>157.4844610276462</v>
+        <v>-150.0517248873528</v>
       </c>
       <c r="N7" t="n">
-        <v>18.60450150452391</v>
+        <v>17.86422720767047</v>
       </c>
       <c r="O7" t="n">
         <v>30</v>
       </c>
       <c r="P7" t="n">
-        <v>-139.170853700966</v>
+        <v>-139.9111279978195</v>
       </c>
       <c r="Q7" t="n">
-        <v>-139.170853700966</v>
+        <v>-139.9111279978195</v>
       </c>
       <c r="R7" t="n">
         <v>3995.820130571773</v>
@@ -1041,7 +1041,7 @@
         <v>7.535691564097316</v>
       </c>
       <c r="Y7" t="n">
-        <v>163.8660027232646</v>
+        <v>164.8660027232646</v>
       </c>
       <c r="Z7" t="n">
         <v>1.376276688121171</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>49.27479638867542</v>
+        <v>48.67137204201632</v>
       </c>
       <c r="G8" t="n">
-        <v>46.26449643203561</v>
+        <v>45.66107208537651</v>
       </c>
       <c r="H8" t="n">
         <v>1e-30</v>
@@ -1078,28 +1078,28 @@
         <v>2883.99926371206</v>
       </c>
       <c r="J8" t="n">
-        <v>48.43037103985215</v>
+        <v>47.82694669319304</v>
       </c>
       <c r="K8" t="n">
         <v>187.7547135142475</v>
       </c>
       <c r="L8" t="n">
-        <v>1.099370235910558</v>
+        <v>1.162499108762441</v>
       </c>
       <c r="M8" t="n">
-        <v>157.4719112340601</v>
+        <v>-150.1670737507406</v>
       </c>
       <c r="N8" t="n">
-        <v>18.43037103985215</v>
+        <v>17.82694669319305</v>
       </c>
       <c r="O8" t="n">
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>-139.3243424743954</v>
+        <v>-139.9277668210545</v>
       </c>
       <c r="Q8" t="n">
-        <v>-139.3243424743954</v>
+        <v>-139.9277668210545</v>
       </c>
       <c r="R8" t="n">
         <v>4002.007441609711</v>
@@ -1123,10 +1123,10 @@
         <v>7.535702435525813</v>
       </c>
       <c r="Y8" t="n">
-        <v>163.844312670568</v>
+        <v>164.844312670568</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.440964134184441</v>
+        <v>1.440964134184429</v>
       </c>
     </row>
     <row r="9">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>48.93895494492234</v>
+        <v>48.61961674577355</v>
       </c>
       <c r="G9" t="n">
-        <v>45.92865498828253</v>
+        <v>45.60931678913374</v>
       </c>
       <c r="H9" t="n">
         <v>1e-30</v>
@@ -1160,28 +1160,28 @@
         <v>2877.137587391191</v>
       </c>
       <c r="J9" t="n">
-        <v>48.07383930771423</v>
+        <v>47.75450110856544</v>
       </c>
       <c r="K9" t="n">
         <v>187.7340232258627</v>
       </c>
       <c r="L9" t="n">
-        <v>1.102327855218203</v>
+        <v>1.163816251673528</v>
       </c>
       <c r="M9" t="n">
-        <v>157.4594129107516</v>
+        <v>-150.2830213071709</v>
       </c>
       <c r="N9" t="n">
-        <v>18.07383930771424</v>
+        <v>17.75450110856544</v>
       </c>
       <c r="O9" t="n">
         <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>-139.6601839181484</v>
+        <v>-139.9795221172972</v>
       </c>
       <c r="Q9" t="n">
-        <v>-139.6601839181484</v>
+        <v>-139.9795221172972</v>
       </c>
       <c r="R9" t="n">
         <v>4008.190129797132</v>
@@ -1205,7 +1205,7 @@
         <v>7.535713319009808</v>
       </c>
       <c r="Y9" t="n">
-        <v>163.8225320244808</v>
+        <v>164.8225320244808</v>
       </c>
       <c r="Z9" t="n">
         <v>1.505817370914526</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>48.40247651526845</v>
+        <v>48.53102666283046</v>
       </c>
       <c r="G10" t="n">
-        <v>45.39217655862864</v>
+        <v>45.52072670619064</v>
       </c>
       <c r="H10" t="n">
         <v>1e-30</v>
@@ -1242,28 +1242,28 @@
         <v>2870.276112097037</v>
       </c>
       <c r="J10" t="n">
-        <v>47.51662179485197</v>
+        <v>47.64517194241397</v>
       </c>
       <c r="K10" t="n">
         <v>187.7132841426543</v>
       </c>
       <c r="L10" t="n">
-        <v>1.105306930137825</v>
+        <v>1.165148920056785</v>
       </c>
       <c r="M10" t="n">
-        <v>157.4469758157683</v>
+        <v>-150.3995624440689</v>
       </c>
       <c r="N10" t="n">
-        <v>17.51662179485197</v>
+        <v>17.64517194241397</v>
       </c>
       <c r="O10" t="n">
         <v>30</v>
       </c>
       <c r="P10" t="n">
-        <v>-140.1966623478023</v>
+        <v>-140.0681122002403</v>
       </c>
       <c r="Q10" t="n">
-        <v>-140.1966623478023</v>
+        <v>-140.0681122002403</v>
       </c>
       <c r="R10" t="n">
         <v>4014.36818737927</v>
@@ -1287,7 +1287,7 @@
         <v>7.535724214513424</v>
       </c>
       <c r="Y10" t="n">
-        <v>163.8006601567133</v>
+        <v>164.8006601567133</v>
       </c>
       <c r="Z10" t="n">
         <v>1.570837630214003</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>47.63493091076374</v>
+        <v>48.40350864141762</v>
       </c>
       <c r="G11" t="n">
-        <v>44.62463095412392</v>
+        <v>45.3932086847778</v>
       </c>
       <c r="H11" t="n">
         <v>1e-30</v>
@@ -1324,28 +1324,28 @@
         <v>2863.414845575346</v>
       </c>
       <c r="J11" t="n">
-        <v>46.72828810369529</v>
+        <v>47.49686583434917</v>
       </c>
       <c r="K11" t="n">
         <v>187.6924960560023</v>
       </c>
       <c r="L11" t="n">
-        <v>1.108307700015986</v>
+        <v>1.166497212243613</v>
       </c>
       <c r="M11" t="n">
-        <v>157.4345922858724</v>
+        <v>-150.5167050417432</v>
       </c>
       <c r="N11" t="n">
-        <v>16.72828810369529</v>
+        <v>17.49686583434917</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>-140.964207952307</v>
+        <v>-140.1956302216532</v>
       </c>
       <c r="Q11" t="n">
-        <v>-140.964207952307</v>
+        <v>-140.1956302216532</v>
       </c>
       <c r="R11" t="n">
         <v>4020.541608337709</v>
@@ -1369,10 +1369,10 @@
         <v>7.535735122000748</v>
       </c>
       <c r="Y11" t="n">
-        <v>163.778696257454</v>
+        <v>164.778696257454</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.636026123521763</v>
+        <v>1.636026123521776</v>
       </c>
     </row>
     <row r="12">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.58690259753228</v>
+        <v>48.23450557908203</v>
       </c>
       <c r="G12" t="n">
-        <v>43.57660264089247</v>
+        <v>45.22420562244222</v>
       </c>
       <c r="H12" t="n">
         <v>1e-30</v>
@@ -1406,28 +1406,28 @@
         <v>2856.553798894191</v>
       </c>
       <c r="J12" t="n">
-        <v>45.65942250041584</v>
+        <v>47.3070254819656</v>
       </c>
       <c r="K12" t="n">
         <v>187.6716587659544</v>
       </c>
       <c r="L12" t="n">
-        <v>1.111330370797694</v>
+        <v>1.167861335735925</v>
       </c>
       <c r="M12" t="n">
-        <v>157.4222631025538</v>
+        <v>-150.6344506793617</v>
       </c>
       <c r="N12" t="n">
-        <v>15.65942250041584</v>
+        <v>17.3070254819656</v>
       </c>
       <c r="O12" t="n">
         <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>-142.0122362655385</v>
+        <v>-140.3646332839888</v>
       </c>
       <c r="Q12" t="n">
-        <v>-142.0122362655385</v>
+        <v>-140.3646332839888</v>
       </c>
       <c r="R12" t="n">
         <v>4026.710384922465</v>
@@ -1451,7 +1451,7 @@
         <v>7.535746041435837</v>
       </c>
       <c r="Y12" t="n">
-        <v>163.75663950775</v>
+        <v>164.75663950775</v>
       </c>
       <c r="Z12" t="n">
         <v>1.70138407432339</v>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45.17572685151413</v>
+        <v>48.02089266946246</v>
       </c>
       <c r="G13" t="n">
-        <v>42.16542689487432</v>
+        <v>45.01059271282265</v>
       </c>
       <c r="H13" t="n">
         <v>1e-30</v>
@@ -1488,28 +1488,28 @@
         <v>2849.69298209137</v>
       </c>
       <c r="J13" t="n">
-        <v>44.22736005651052</v>
+        <v>47.07252587445885</v>
       </c>
       <c r="K13" t="n">
         <v>187.6507720680672</v>
       </c>
       <c r="L13" t="n">
-        <v>1.114375122855263</v>
+        <v>1.169241578377575</v>
       </c>
       <c r="M13" t="n">
-        <v>157.4099952557694</v>
+        <v>-150.7527961725172</v>
       </c>
       <c r="N13" t="n">
-        <v>14.22736005651052</v>
+        <v>17.07252587445886</v>
       </c>
       <c r="O13" t="n">
         <v>30</v>
       </c>
       <c r="P13" t="n">
-        <v>-143.4234120115567</v>
+        <v>-140.5782461936083</v>
       </c>
       <c r="Q13" t="n">
-        <v>-143.4234120115567</v>
+        <v>-140.5782461936083</v>
       </c>
       <c r="R13" t="n">
         <v>4032.874509990546</v>
@@ -1533,10 +1533,10 @@
         <v>7.535756972782754</v>
       </c>
       <c r="Y13" t="n">
-        <v>163.7344892568628</v>
+        <v>164.7344892568628</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.766912749526267</v>
+        <v>1.76691274952628</v>
       </c>
     </row>
     <row r="14">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>43.25248558558114</v>
+        <v>47.75887217675156</v>
       </c>
       <c r="G14" t="n">
-        <v>40.24218562894133</v>
+        <v>44.74857222011175</v>
       </c>
       <c r="H14" t="n">
         <v>1e-30</v>
@@ -1570,28 +1570,28 @@
         <v>2842.83240638419</v>
       </c>
       <c r="J14" t="n">
-        <v>42.283182482619</v>
+        <v>46.78956907378942</v>
       </c>
       <c r="K14" t="n">
         <v>187.6298357601086</v>
       </c>
       <c r="L14" t="n">
-        <v>1.117442165797901</v>
+        <v>1.170638153276563</v>
       </c>
       <c r="M14" t="n">
-        <v>157.3977895653996</v>
+        <v>-150.8717429382813</v>
       </c>
       <c r="N14" t="n">
-        <v>12.28318248261901</v>
+        <v>16.78956907378943</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>-145.3466532774897</v>
+        <v>-140.8402666863192</v>
       </c>
       <c r="Q14" t="n">
-        <v>-145.3466532774897</v>
+        <v>-140.8402666863192</v>
       </c>
       <c r="R14" t="n">
         <v>4039.03397581495</v>
@@ -1615,10 +1615,10 @@
         <v>7.535767916005519</v>
       </c>
       <c r="Y14" t="n">
-        <v>163.7122446700199</v>
+        <v>164.7122446700199</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.832613395866888</v>
+        <v>1.832613395866875</v>
       </c>
     </row>
     <row r="15">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>40.51121002605002</v>
+        <v>47.44381157907376</v>
       </c>
       <c r="G15" t="n">
-        <v>37.5009100694102</v>
+        <v>44.43351162243395</v>
       </c>
       <c r="H15" t="n">
         <v>1e-30</v>
@@ -1652,28 +1652,28 @@
         <v>2835.972079826671</v>
       </c>
       <c r="J15" t="n">
-        <v>39.52092079176672</v>
+        <v>46.45352234479047</v>
       </c>
       <c r="K15" t="n">
         <v>187.6088496287875</v>
       </c>
       <c r="L15" t="n">
-        <v>1.120531736829488</v>
+        <v>1.172051208015542</v>
       </c>
       <c r="M15" t="n">
-        <v>157.3856413793383</v>
+        <v>-150.9912965722239</v>
       </c>
       <c r="N15" t="n">
-        <v>9.520920791766724</v>
+        <v>16.45352234479047</v>
       </c>
       <c r="O15" t="n">
         <v>30</v>
       </c>
       <c r="P15" t="n">
-        <v>-148.0879288370208</v>
+        <v>-141.155327283997</v>
       </c>
       <c r="Q15" t="n">
-        <v>-148.0879288370208</v>
+        <v>-141.155327283997</v>
       </c>
       <c r="R15" t="n">
         <v>4045.188776384386</v>
@@ -1697,10 +1697,10 @@
         <v>7.535778871068056</v>
       </c>
       <c r="Y15" t="n">
-        <v>163.6899049626078</v>
+        <v>164.6899049626078</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8984872830552</v>
+        <v>1.898487283055213</v>
       </c>
     </row>
     <row r="16">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36.15100117448441</v>
+        <v>47.06997936805196</v>
       </c>
       <c r="G16" t="n">
-        <v>33.14070121784459</v>
+        <v>44.05967941141215</v>
       </c>
       <c r="H16" t="n">
         <v>1e-30</v>
@@ -1734,28 +1734,28 @@
         <v>2829.112013780766</v>
       </c>
       <c r="J16" t="n">
-        <v>35.13967578090498</v>
+        <v>46.05865397447254</v>
       </c>
       <c r="K16" t="n">
         <v>187.5878134694914</v>
       </c>
       <c r="L16" t="n">
-        <v>1.123644050869024</v>
+        <v>1.173480961376502</v>
       </c>
       <c r="M16" t="n">
-        <v>157.3735515197613</v>
+        <v>-151.1114584696585</v>
       </c>
       <c r="N16" t="n">
-        <v>5.139675780904984</v>
+        <v>16.05865397447254</v>
       </c>
       <c r="O16" t="n">
         <v>30</v>
       </c>
       <c r="P16" t="n">
-        <v>-152.4481376885864</v>
+        <v>-141.5291594950188</v>
       </c>
       <c r="Q16" t="n">
-        <v>-152.4481376885864</v>
+        <v>-141.5291594950188</v>
       </c>
       <c r="R16" t="n">
         <v>4051.338903992383</v>
@@ -1779,10 +1779,10 @@
         <v>7.53578983793435</v>
       </c>
       <c r="Y16" t="n">
-        <v>163.6674692819926</v>
+        <v>164.6674692819926</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.964535681859003</v>
+        <v>1.964535681859015</v>
       </c>
     </row>
     <row r="17">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26.33567140190044</v>
+        <v>46.63018328114912</v>
       </c>
       <c r="G17" t="n">
-        <v>23.32537144526063</v>
+        <v>43.6198833245093</v>
       </c>
       <c r="H17" t="n">
         <v>1e-30</v>
@@ -1816,28 +1816,28 @@
         <v>2822.252219716514</v>
       </c>
       <c r="J17" t="n">
-        <v>25.30325961537828</v>
+        <v>45.59777149462695</v>
       </c>
       <c r="K17" t="n">
         <v>187.5667270765487</v>
       </c>
       <c r="L17" t="n">
-        <v>1.126779284793705</v>
+        <v>1.174927749139475</v>
       </c>
       <c r="M17" t="n">
-        <v>157.3615298817034</v>
+        <v>-151.232223019358</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.696740384621717</v>
+        <v>15.59777149462695</v>
       </c>
       <c r="O17" t="n">
         <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>-162.2634674611703</v>
+        <v>-141.9689555819217</v>
       </c>
       <c r="Q17" t="n">
-        <v>-162.2634674611703</v>
+        <v>-141.9689555819217</v>
       </c>
       <c r="R17" t="n">
         <v>4057.484350918837</v>
@@ -1861,10 +1861,10 @@
         <v>7.535800816568286</v>
       </c>
       <c r="Y17" t="n">
-        <v>163.6449369459386</v>
+        <v>164.6449369459386</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.030759907970641</v>
+        <v>2.030759907970616</v>
       </c>
     </row>
     <row r="18">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27.37066818327738</v>
+        <v>46.11539262101832</v>
       </c>
       <c r="G18" t="n">
-        <v>24.36036822663757</v>
+        <v>43.10509266437851</v>
       </c>
       <c r="H18" t="n">
         <v>1e-30</v>
@@ -1898,28 +1898,28 @@
         <v>2815.392705892127</v>
       </c>
       <c r="J18" t="n">
-        <v>26.31711955318395</v>
+        <v>45.06184399092489</v>
       </c>
       <c r="K18" t="n">
         <v>187.5455902329773</v>
       </c>
       <c r="L18" t="n">
-        <v>1.129937696688128</v>
+        <v>1.176391689615344</v>
       </c>
       <c r="M18" t="n">
-        <v>157.3495688137949</v>
+        <v>-151.3535980331108</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.682880446816053</v>
+        <v>15.0618439909249</v>
       </c>
       <c r="O18" t="n">
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>-161.2284706797934</v>
+        <v>-142.4837462420525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-161.2284706797934</v>
+        <v>-142.4837462420525</v>
       </c>
       <c r="R18" t="n">
         <v>4063.625111191426</v>
@@ -1943,10 +1943,10 @@
         <v>7.535811806933767</v>
       </c>
       <c r="Y18" t="n">
-        <v>163.6223070849084</v>
+        <v>164.6223070849084</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.097161257011621</v>
+        <v>2.097161257011583</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>36.53329287772444</v>
+        <v>45.51393602263047</v>
       </c>
       <c r="G19" t="n">
-        <v>33.52299292108463</v>
+        <v>42.50363606599066</v>
       </c>
       <c r="H19" t="n">
         <v>1e-30</v>
@@ -1980,28 +1980,28 @@
         <v>2808.533483950788</v>
       </c>
       <c r="J19" t="n">
-        <v>35.45855674540703</v>
+        <v>44.43919989031307</v>
       </c>
       <c r="K19" t="n">
         <v>187.5244027307534</v>
       </c>
       <c r="L19" t="n">
-        <v>1.133119509609639</v>
+        <v>1.177873011135992</v>
       </c>
       <c r="M19" t="n">
-        <v>157.337669170247</v>
+        <v>-151.475584797462</v>
       </c>
       <c r="N19" t="n">
-        <v>5.458556745407028</v>
+        <v>14.43919989031307</v>
       </c>
       <c r="O19" t="n">
         <v>30</v>
       </c>
       <c r="P19" t="n">
-        <v>-152.0658459853464</v>
+        <v>-143.0852028404403</v>
       </c>
       <c r="Q19" t="n">
-        <v>-152.0658459853464</v>
+        <v>-143.0852028404403</v>
       </c>
       <c r="R19" t="n">
         <v>4069.761177089858</v>
@@ -2025,10 +2025,10 @@
         <v>7.535822808994611</v>
       </c>
       <c r="Y19" t="n">
-        <v>163.5995788196273</v>
+        <v>164.5995788196273</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.163741037189362</v>
+        <v>2.16374103718935</v>
       </c>
     </row>
     <row r="20">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40.78082818163804</v>
+        <v>44.81040128858833</v>
       </c>
       <c r="G20" t="n">
-        <v>37.77052822499824</v>
+        <v>41.80010133194852</v>
       </c>
       <c r="H20" t="n">
         <v>1e-30</v>
@@ -2062,28 +2062,28 @@
         <v>2801.674564497573</v>
       </c>
       <c r="J20" t="n">
-        <v>39.68485367577899</v>
+        <v>43.71442678272928</v>
       </c>
       <c r="K20" t="n">
         <v>187.5031643572117</v>
       </c>
       <c r="L20" t="n">
-        <v>1.136324919984267</v>
+        <v>1.179372023127835</v>
       </c>
       <c r="M20" t="n">
-        <v>157.3258380596666</v>
+        <v>-151.598179671018</v>
       </c>
       <c r="N20" t="n">
-        <v>9.684853675778992</v>
+        <v>13.71442678272927</v>
       </c>
       <c r="O20" t="n">
         <v>30</v>
       </c>
       <c r="P20" t="n">
-        <v>-147.8183106814327</v>
+        <v>-143.7887375744824</v>
       </c>
       <c r="Q20" t="n">
-        <v>-147.8183106814327</v>
+        <v>-143.7887375744824</v>
       </c>
       <c r="R20" t="n">
         <v>4075.89254150259</v>
@@ -2107,10 +2107,10 @@
         <v>7.535833822714661</v>
       </c>
       <c r="Y20" t="n">
-        <v>163.5767514431665</v>
+        <v>164.5767514431665</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.230500602020816</v>
+        <v>2.230500602020829</v>
       </c>
     </row>
     <row r="21">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43.47940772206555</v>
+        <v>43.98396609538463</v>
       </c>
       <c r="G21" t="n">
-        <v>40.46910776542573</v>
+        <v>40.97366613874482</v>
       </c>
       <c r="H21" t="n">
         <v>1e-30</v>
@@ -2144,28 +2144,28 @@
         <v>2794.815959315634</v>
       </c>
       <c r="J21" t="n">
-        <v>42.36214376087653</v>
+        <v>42.86670213419562</v>
       </c>
       <c r="K21" t="n">
         <v>187.4818749018818</v>
       </c>
       <c r="L21" t="n">
-        <v>1.139554155466925</v>
+        <v>1.180888960356702</v>
       </c>
       <c r="M21" t="n">
-        <v>157.314076374624</v>
+        <v>-151.7213837809292</v>
       </c>
       <c r="N21" t="n">
-        <v>12.36214376087653</v>
+        <v>12.86670213419562</v>
       </c>
       <c r="O21" t="n">
         <v>30</v>
       </c>
       <c r="P21" t="n">
-        <v>-145.1197311410052</v>
+        <v>-144.6151727676861</v>
       </c>
       <c r="Q21" t="n">
-        <v>-145.1197311410052</v>
+        <v>-144.6151727676861</v>
       </c>
       <c r="R21" t="n">
         <v>4082.019196753073</v>
@@ -2189,10 +2189,10 @@
         <v>7.535844848057712</v>
       </c>
       <c r="Y21" t="n">
-        <v>163.5538240585597</v>
+        <v>164.5538240585597</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.297441285608205</v>
+        <v>2.297441285608218</v>
       </c>
     </row>
     <row r="22">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>45.37469020776651</v>
+        <v>43.00552353582104</v>
       </c>
       <c r="G22" t="n">
-        <v>42.36439025112669</v>
+        <v>39.99522357918123</v>
       </c>
       <c r="H22" t="n">
         <v>1e-30</v>
@@ -2226,28 +2226,28 @@
         <v>2787.957677020446</v>
       </c>
       <c r="J22" t="n">
-        <v>44.23608548767525</v>
+        <v>41.86691881572978</v>
       </c>
       <c r="K22" t="n">
         <v>187.4605341429796</v>
       </c>
       <c r="L22" t="n">
-        <v>1.142807471706345</v>
+        <v>1.182423991447942</v>
       </c>
       <c r="M22" t="n">
-        <v>157.3023795019968</v>
+        <v>-151.8452025245903</v>
       </c>
       <c r="N22" t="n">
-        <v>14.23608548767525</v>
+        <v>11.86691881572978</v>
       </c>
       <c r="O22" t="n">
         <v>30</v>
       </c>
       <c r="P22" t="n">
-        <v>-143.2244486553043</v>
+        <v>-145.5936153272498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-143.2244486553043</v>
+        <v>-145.5936153272498</v>
       </c>
       <c r="R22" t="n">
         <v>4088.141136855705</v>
@@ -2271,10 +2271,10 @@
         <v>7.535855884987495</v>
       </c>
       <c r="Y22" t="n">
-        <v>163.5307958202829</v>
+        <v>164.5307958202829</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.364564445292857</v>
+        <v>2.364564445292896</v>
       </c>
     </row>
     <row r="23">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>46.75464924637926</v>
+        <v>41.83246654017373</v>
       </c>
       <c r="G23" t="n">
-        <v>43.74434928973945</v>
+        <v>38.82216658353392</v>
       </c>
       <c r="H23" t="n">
         <v>1e-30</v>
@@ -2308,28 +2308,28 @@
         <v>2781.099729570777</v>
       </c>
       <c r="J23" t="n">
-        <v>45.5946522509162</v>
+        <v>40.67246954471067</v>
       </c>
       <c r="K23" t="n">
         <v>187.4391418676077</v>
       </c>
       <c r="L23" t="n">
-        <v>1.146085102212184</v>
+        <v>1.183977357516207</v>
       </c>
       <c r="M23" t="n">
-        <v>157.2907483404074</v>
+        <v>-151.9696369935887</v>
       </c>
       <c r="N23" t="n">
-        <v>15.59465225091619</v>
+        <v>10.67246954471067</v>
       </c>
       <c r="O23" t="n">
         <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>-141.8444896166915</v>
+        <v>-146.7666723228971</v>
       </c>
       <c r="Q23" t="n">
-        <v>-141.8444896166915</v>
+        <v>-146.7666723228971</v>
       </c>
       <c r="R23" t="n">
         <v>4094.258354138889</v>
@@ -2353,7 +2353,7 @@
         <v>7.535866933467747</v>
       </c>
       <c r="Y23" t="n">
-        <v>163.5076658118871</v>
+        <v>164.5076658118871</v>
       </c>
       <c r="Z23" t="n">
         <v>2.431871441127968</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>47.75832373920274</v>
+        <v>40.39873128022811</v>
       </c>
       <c r="G24" t="n">
-        <v>44.74802378256293</v>
+        <v>37.38843132358829</v>
       </c>
       <c r="H24" t="n">
         <v>1e-30</v>
@@ -2390,28 +2390,28 @@
         <v>2774.242129006447</v>
       </c>
       <c r="J24" t="n">
-        <v>46.57688273778849</v>
+        <v>39.21729027881386</v>
       </c>
       <c r="K24" t="n">
         <v>187.4176978616566</v>
       </c>
       <c r="L24" t="n">
-        <v>1.149387239871286</v>
+        <v>1.185549416955846</v>
       </c>
       <c r="M24" t="n">
-        <v>157.2791929223854</v>
+        <v>-152.0946810013168</v>
       </c>
       <c r="N24" t="n">
-        <v>16.57688273778849</v>
+        <v>9.217290278813861</v>
       </c>
       <c r="O24" t="n">
         <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>-140.8408151238681</v>
+        <v>-148.2004075828427</v>
       </c>
       <c r="Q24" t="n">
-        <v>-140.8408151238681</v>
+        <v>-148.2004075828427</v>
       </c>
       <c r="R24" t="n">
         <v>4100.370840948545</v>
@@ -2435,7 +2435,7 @@
         <v>7.535877993462202</v>
       </c>
       <c r="Y24" t="n">
-        <v>163.4844332917572</v>
+        <v>164.4844332917572</v>
       </c>
       <c r="Z24" t="n">
         <v>2.499363679460075</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>48.46058160268193</v>
+        <v>38.59404828879218</v>
       </c>
       <c r="G25" t="n">
-        <v>45.45028164604211</v>
+        <v>35.58374833215237</v>
       </c>
       <c r="H25" t="n">
         <v>1e-30</v>
@@ -2472,28 +2472,28 @@
         <v>2767.384884207488</v>
       </c>
       <c r="J25" t="n">
-        <v>47.25764463923252</v>
+        <v>37.39111132534277</v>
       </c>
       <c r="K25" t="n">
         <v>187.3962018996214</v>
       </c>
       <c r="L25" t="n">
-        <v>1.152714163694703</v>
+        <v>1.187140310542884</v>
       </c>
       <c r="M25" t="n">
-        <v>157.2677056181326</v>
+        <v>-152.2203422558704</v>
       </c>
       <c r="N25" t="n">
-        <v>17.25764463923252</v>
+        <v>7.391111325342766</v>
       </c>
       <c r="O25" t="n">
         <v>30</v>
       </c>
       <c r="P25" t="n">
-        <v>-140.1385572603889</v>
+        <v>-150.0050905742786</v>
       </c>
       <c r="Q25" t="n">
-        <v>-140.1385572603889</v>
+        <v>-150.0050905742786</v>
       </c>
       <c r="R25" t="n">
         <v>4106.478591302091</v>
@@ -2517,7 +2517,7 @@
         <v>7.535889064934467</v>
       </c>
       <c r="Y25" t="n">
-        <v>163.46109732498</v>
+        <v>164.46109732498</v>
       </c>
       <c r="Z25" t="n">
         <v>2.567042547016642</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>48.90297928069855</v>
+        <v>36.21179632846653</v>
       </c>
       <c r="G26" t="n">
-        <v>45.89267932405873</v>
+        <v>33.20149637182671</v>
       </c>
       <c r="H26" t="n">
         <v>1e-30</v>
@@ -2554,28 +2554,28 @@
         <v>2760.528007384252</v>
       </c>
       <c r="J26" t="n">
-        <v>47.67849418251469</v>
+        <v>34.98731123028267</v>
       </c>
       <c r="K26" t="n">
         <v>187.3746537648869</v>
       </c>
       <c r="L26" t="n">
-        <v>1.156066115016399</v>
+        <v>1.188750289191088</v>
       </c>
       <c r="M26" t="n">
-        <v>157.256287360568</v>
+        <v>-152.3466216753879</v>
       </c>
       <c r="N26" t="n">
-        <v>17.67849418251469</v>
+        <v>4.98731123028267</v>
       </c>
       <c r="O26" t="n">
         <v>30</v>
       </c>
       <c r="P26" t="n">
-        <v>-139.6961595823722</v>
+        <v>-152.3873425346043</v>
       </c>
       <c r="Q26" t="n">
-        <v>-139.6961595823722</v>
+        <v>-152.3873425346043</v>
       </c>
       <c r="R26" t="n">
         <v>4112.581597560728</v>
@@ -2599,10 +2599,10 @@
         <v>7.535900147848222</v>
       </c>
       <c r="Y26" t="n">
-        <v>163.4376569660906</v>
+        <v>164.4376569660906</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.634909443945255</v>
+        <v>2.63490944394523</v>
       </c>
     </row>
   </sheetData>
